--- a/data/trans_bre/IP41-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Edad-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 8,24</t>
+          <t>-2,02; 8,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 7,35</t>
+          <t>-1,8; 8,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 7,21</t>
+          <t>-6,36; 7,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 9,41</t>
+          <t>-2,12; 9,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 8,25</t>
+          <t>-1,92; 9,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 8,45</t>
+          <t>-6,94; 8,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 1,62</t>
+          <t>-6,12; 1,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,34</t>
+          <t>-6,6; 2,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,72</t>
+          <t>-1,56; 9,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 1,75</t>
+          <t>-6,55; 1,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,86</t>
+          <t>-7,24; 3,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 10,87</t>
+          <t>-1,85; 11,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -0,41</t>
+          <t>-13,31; -0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,56</t>
+          <t>-6,19; 5,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 4,08</t>
+          <t>-9,09; 4,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -0,54</t>
+          <t>-14,11; -0,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 6,58</t>
+          <t>-6,81; 6,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 5,22</t>
+          <t>-10,77; 5,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,29</t>
+          <t>-3,26; 5,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 10,22</t>
+          <t>-1,87; 9,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 6,68</t>
+          <t>-7,57; 6,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,92</t>
+          <t>-3,46; 6,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 12,93</t>
+          <t>-2,15; 12,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 8,22</t>
+          <t>-8,7; 8,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,97</t>
+          <t>-3,64; 0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,82</t>
+          <t>-1,75; 3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,35</t>
+          <t>-2,79; 3,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,06</t>
+          <t>-3,91; 1,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,4</t>
+          <t>-1,98; 4,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 4,0</t>
+          <t>-3,27; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">

--- a/data/trans_bre/IP41-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Edad-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 8,32</t>
+          <t>-1,86; 8,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 8,33</t>
+          <t>-1,9; 7,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,11</t>
+          <t>-5,63; 7,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,97; 9,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 9,43</t>
+          <t>-2,0; 8,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 9,54</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-6,94; 8,4</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,14; 8,89</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-2,43%</t>
+          <t>-1,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,66</t>
+          <t>-6,25; 1,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,96</t>
+          <t>-6,64; 2,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 9,57</t>
+          <t>-2,37; 8,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,59; 1,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 1,72</t>
+          <t>-7,32; 3,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 3,39</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-1,85; 11,98</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-2,79; 10,7</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-7,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-7,51%</t>
+          <t>-0,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>-2,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -0,8</t>
+          <t>-13,64; -1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 5,25</t>
+          <t>-6,59; 5,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 4,38</t>
+          <t>-8,87; 4,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,44; -1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -0,89</t>
+          <t>-7,27; 6,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 6,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-10,77; 5,51</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,6; 5,93</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>-0,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,8</t>
+          <t>-3,2; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 9,91</t>
+          <t>-1,58; 9,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 6,89</t>
+          <t>-7,65; 6,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,36; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 6,5</t>
+          <t>-1,77; 12,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 12,3</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,7; 8,66</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,66; 8,58</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-1,4%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,99</t>
+          <t>-3,82; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,55</t>
+          <t>-1,75; 3,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,94</t>
+          <t>-2,75; 3,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,11; 1,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,07</t>
+          <t>-1,92; 4,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,08</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 4,83</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-3,22; 4,73</t>
         </is>
       </c>
     </row>
@@ -1108,12 +992,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
   </mergeCells>

--- a/data/trans_bre/IP41-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 8,33</t>
+          <t>-1,7; 8,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,79</t>
+          <t>-1,96; 7,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 7,57</t>
+          <t>-5,5; 7,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 9,52</t>
+          <t>-1,74; 9,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 8,76</t>
+          <t>-2,1; 8,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 8,89</t>
+          <t>-6,12; 8,45</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,61</t>
+          <t>-6,41; 1,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 2,92</t>
+          <t>-6,09; 3,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 8,63</t>
+          <t>-2,31; 8,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 1,78</t>
+          <t>-6,8; 1,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,32</t>
+          <t>-6,62; 3,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 10,7</t>
+          <t>-2,68; 10,87</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -1,41</t>
+          <t>-12,93; -0,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 5,78</t>
+          <t>-6,69; 5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 4,61</t>
+          <t>-9,43; 4,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; -1,57</t>
+          <t>-13,79; -0,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 6,77</t>
+          <t>-7,23; 6,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 5,93</t>
+          <t>-11,14; 5,22</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,53</t>
+          <t>-3,29; 5,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 9,74</t>
+          <t>-2,19; 10,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 6,9</t>
+          <t>-7,21; 6,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 6,15</t>
+          <t>-3,46; 5,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 12,26</t>
+          <t>-2,45; 12,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 8,58</t>
+          <t>-8,29; 8,22</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,04</t>
+          <t>-3,81; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,58</t>
+          <t>-1,89; 3,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,89</t>
+          <t>-2,81; 3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 1,13</t>
+          <t>-4,06; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,14</t>
+          <t>-2,11; 4,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,73</t>
+          <t>-3,31; 4,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP41-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.195604845067401</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.814709735706078</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6017768718167837</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.03481865676340829</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.03085303090427986</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.006831290745945302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,7; 8,24</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,96; 7,35</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,5; 7,21</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-1,74; 9,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 8,25</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-6,12; 8,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.70394922627936</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.955298334865031</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.504052016780903</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.01744066291387917</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.02098959164211102</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.06121122063853763</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.236162782180275</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.352662750455432</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.210525354774281</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.09408780355664613</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.08254667612925282</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.08452921621044991</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,35</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,41; 1,62</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,09; 3,34</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,31; 8,72</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,8; 1,75</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-6,62; 3,86</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-2,68; 10,87</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.261874771560679</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.575988757521785</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.346304393656307</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.02432623620893362</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01763681838732457</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.04018525277002684</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-6,93</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,71%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.411024025242906</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.087460106211337</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.309303367021559</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.0680376832293898</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.06617970063380736</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.02682206553284786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,93; -0,41</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,69; 5,56</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,43; 4,08</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-13,79; -0,54</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 6,58</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-11,14; 5,22</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.618624603199076</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.340007848009015</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.722226306431798</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.01753187699201461</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03858001302182767</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1086508361596609</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,79%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-6.925015106122312</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.6507250319561453</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.21407670665773</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.07505305862266271</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.007331117366448608</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02712504647955774</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,29; 5,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,19; 10,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,21; 6,68</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,46; 5,92</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 12,93</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-8,29; 8,22</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.92522400344892</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.685876850900583</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-9.429545533251861</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.1378614288826008</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.07229113729419458</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1114429019534527</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.4080627067617892</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.560050945546967</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.080540353272639</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-0.005439898722966107</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.06577283484056692</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.05222386685786477</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.163088597410589</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.013001356427315</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.6596352949112205</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.01263112149191661</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.04784724478371978</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.007883060624796535</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.289939424202436</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.194964748583568</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.209731761416817</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.03456103809829333</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.02450456276948932</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.08291037480009182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.294321433148299</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.22322340233302</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.683932750343151</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.05916235002039028</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1293399223072557</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.08216967555312912</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,4%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 0,97</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 3,82</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,81; 3,35</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 1,06</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 4,4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 4,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.291350389372303</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.887488743761522</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.438067261686359</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.01397804185036947</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.01005256970818911</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.005230318811633617</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.807112858259318</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.890082802216952</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.810084340435331</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.04060615843134109</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.02114604784160384</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.03313003466145011</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9670390298034258</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.823869576491322</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.349075401492358</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.01059845365509916</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.04397412199349154</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.03997637458596782</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
